--- a/set.xlsx
+++ b/set.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoro\Downloads\ped\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\skoro\Downloads\Product_Basket\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -222,13 +223,16 @@
   </si>
   <si>
     <t>это просто сумма на неделю</t>
+  </si>
+  <si>
+    <t>сумма в месяц на продукты</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +244,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -264,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -273,6 +284,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -294,16 +308,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>681990</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -320,7 +334,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5486400" y="0"/>
+          <a:off x="0" y="0"/>
           <a:ext cx="7524750" cy="5619750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -332,16 +346,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1047750</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -358,7 +372,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6096000" y="6766560"/>
+          <a:off x="609600" y="6766560"/>
           <a:ext cx="7524750" cy="5619750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -634,10 +648,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +674,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -683,7 +697,7 @@
         <v>-6254.6899999999987</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -705,11 +719,8 @@
       <c r="G3" s="3">
         <v>-6000.1699999999983</v>
       </c>
-      <c r="W3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -732,7 +743,7 @@
         <v>-7776.3500000000022</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -755,7 +766,7 @@
         <v>-6849.0538461538454</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -778,7 +789,7 @@
         <v>-8413.4900000000016</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -801,7 +812,7 @@
         <v>-7680.9769230769234</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -824,7 +835,7 @@
         <v>-6508.7900000000009</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -847,7 +858,7 @@
         <v>-6643.9000000000015</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -870,7 +881,7 @@
         <v>-5121.9500000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -893,7 +904,7 @@
         <v>-4610.7769230769245</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -916,7 +927,7 @@
         <v>-5624.2692307692305</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -939,7 +950,7 @@
         <v>-7142.57</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -962,7 +973,7 @@
         <v>-5043.8299999999981</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -984,11 +995,8 @@
       <c r="G15" s="3">
         <v>-5831.0384615384628</v>
       </c>
-      <c r="X15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>32</v>
       </c>
@@ -1126,7 +1134,7 @@
         <v>-5730.2384615384617</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1561,6 +1569,345 @@
       </c>
       <c r="G40" s="3">
         <v>-7499.4076923076937</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="N1:U40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="20" max="21" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="14:21" ht="72" x14ac:dyDescent="0.3">
+      <c r="T1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="N2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="3">
+        <v>-6254.6899999999987</v>
+      </c>
+      <c r="U2" s="3">
+        <v>19905.689999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T3" s="3">
+        <v>-6000.1699999999983</v>
+      </c>
+      <c r="U3" s="3">
+        <v>19651.169999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T4" s="3">
+        <v>-7776.3500000000022</v>
+      </c>
+      <c r="U4" s="3">
+        <v>21427.350000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T5" s="3">
+        <v>-6849.0538461538454</v>
+      </c>
+      <c r="U5" s="3">
+        <v>16079.053846153845</v>
+      </c>
+    </row>
+    <row r="6" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T6" s="3">
+        <v>-8413.4900000000016</v>
+      </c>
+      <c r="U6" s="3">
+        <v>22064.49</v>
+      </c>
+    </row>
+    <row r="7" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T7" s="3">
+        <v>-7680.9769230769234</v>
+      </c>
+      <c r="U7" s="3">
+        <v>16910.976923076923</v>
+      </c>
+    </row>
+    <row r="8" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T8" s="3">
+        <v>-6508.7900000000009</v>
+      </c>
+      <c r="U8" s="3">
+        <v>20159.79</v>
+      </c>
+    </row>
+    <row r="9" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T9" s="3">
+        <v>-6643.9000000000015</v>
+      </c>
+      <c r="U9" s="3">
+        <v>15873.900000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T10" s="3">
+        <v>-5121.9500000000007</v>
+      </c>
+      <c r="U10" s="3">
+        <v>18772.95</v>
+      </c>
+    </row>
+    <row r="11" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T11" s="3">
+        <v>-4610.7769230769245</v>
+      </c>
+      <c r="U11" s="3">
+        <v>13840.776923076925</v>
+      </c>
+    </row>
+    <row r="12" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T12" s="3">
+        <v>-5624.2692307692305</v>
+      </c>
+      <c r="U12" s="3">
+        <v>14854.26923076923</v>
+      </c>
+    </row>
+    <row r="13" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T13" s="3">
+        <v>-7142.57</v>
+      </c>
+      <c r="U13" s="3">
+        <v>20793.57</v>
+      </c>
+    </row>
+    <row r="14" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T14" s="3">
+        <v>-5043.8299999999981</v>
+      </c>
+      <c r="U14" s="3">
+        <v>18694.829999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T15" s="3">
+        <v>-5831.0384615384628</v>
+      </c>
+      <c r="U15" s="3">
+        <v>15061.038461538463</v>
+      </c>
+    </row>
+    <row r="16" spans="14:21" x14ac:dyDescent="0.3">
+      <c r="T16" s="3">
+        <v>-4147.4846153846174</v>
+      </c>
+      <c r="U16" s="3">
+        <v>13377.484615384617</v>
+      </c>
+    </row>
+    <row r="17" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T17" s="3">
+        <v>-5442.8299999999981</v>
+      </c>
+      <c r="U17" s="3">
+        <v>19093.829999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T18" s="3">
+        <v>-4809.8899999999994</v>
+      </c>
+      <c r="U18" s="3">
+        <v>18460.89</v>
+      </c>
+    </row>
+    <row r="19" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T19" s="3">
+        <v>-5588.57</v>
+      </c>
+      <c r="U19" s="3">
+        <v>19239.57</v>
+      </c>
+    </row>
+    <row r="20" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T20" s="3">
+        <v>-5838.0499999999993</v>
+      </c>
+      <c r="U20" s="3">
+        <v>19489.05</v>
+      </c>
+    </row>
+    <row r="21" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T21" s="3">
+        <v>-5730.2384615384617</v>
+      </c>
+      <c r="U21" s="3">
+        <v>14960.238461538462</v>
+      </c>
+    </row>
+    <row r="22" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T22" s="3">
+        <v>-3846.3769230769249</v>
+      </c>
+      <c r="U22" s="3">
+        <v>13076.376923076925</v>
+      </c>
+    </row>
+    <row r="23" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T23" s="3">
+        <v>-6508.7900000000009</v>
+      </c>
+      <c r="U23" s="3">
+        <v>20159.79</v>
+      </c>
+    </row>
+    <row r="24" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T24" s="3">
+        <v>-6375.23</v>
+      </c>
+      <c r="U24" s="3">
+        <v>20026.23</v>
+      </c>
+    </row>
+    <row r="25" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T25" s="3">
+        <v>-4324.7900000000009</v>
+      </c>
+      <c r="U25" s="3">
+        <v>17975.79</v>
+      </c>
+    </row>
+    <row r="26" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T26" s="3">
+        <v>-2738.4500000000007</v>
+      </c>
+      <c r="U26" s="3">
+        <v>16389.45</v>
+      </c>
+    </row>
+    <row r="27" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T27" s="3">
+        <v>-5548.6699999999983</v>
+      </c>
+      <c r="U27" s="3">
+        <v>19199.669999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T28" s="3">
+        <v>-5403.7699999999968</v>
+      </c>
+      <c r="U28" s="3">
+        <v>19054.769999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T29" s="3">
+        <v>-6960.2900000000009</v>
+      </c>
+      <c r="U29" s="3">
+        <v>20611.29</v>
+      </c>
+    </row>
+    <row r="30" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T30" s="3">
+        <v>-6280.4384615384606</v>
+      </c>
+      <c r="U30" s="3">
+        <v>15510.438461538461</v>
+      </c>
+    </row>
+    <row r="31" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T31" s="3">
+        <v>-4566.2900000000009</v>
+      </c>
+      <c r="U31" s="3">
+        <v>18217.29</v>
+      </c>
+    </row>
+    <row r="32" spans="20:21" x14ac:dyDescent="0.3">
+      <c r="T32" s="3">
+        <v>-5260.4846153846174</v>
+      </c>
+      <c r="U32" s="3">
+        <v>14490.484615384617</v>
+      </c>
+    </row>
+    <row r="33" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="T33" s="3">
+        <v>-6075.6076923076944</v>
+      </c>
+      <c r="U33" s="3">
+        <v>15305.607692307694</v>
+      </c>
+    </row>
+    <row r="34" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="T34" s="3">
+        <v>-6734.3615384615405</v>
+      </c>
+      <c r="U34" s="3">
+        <v>15964.36153846154</v>
+      </c>
+    </row>
+    <row r="35" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="T35" s="3">
+        <v>-7419.6076923076944</v>
+      </c>
+      <c r="U35" s="3">
+        <v>16649.607692307694</v>
+      </c>
+    </row>
+    <row r="36" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="T36" s="3">
+        <v>-7671.2846153846149</v>
+      </c>
+      <c r="U36" s="3">
+        <v>16901.284615384615</v>
+      </c>
+    </row>
+    <row r="37" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="T37" s="3">
+        <v>-5201.0384615384628</v>
+      </c>
+      <c r="U37" s="3">
+        <v>14431.038461538463</v>
+      </c>
+    </row>
+    <row r="38" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="T38" s="3">
+        <v>-6593.1769230769241</v>
+      </c>
+      <c r="U38" s="3">
+        <v>15823.176923076924</v>
+      </c>
+    </row>
+    <row r="39" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P39" t="s">
+        <v>65</v>
+      </c>
+      <c r="T39" s="3">
+        <v>-6262.6692307692301</v>
+      </c>
+      <c r="U39" s="3">
+        <v>15492.66923076923</v>
+      </c>
+    </row>
+    <row r="40" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="T40" s="3">
+        <v>-7499.4076923076937</v>
+      </c>
+      <c r="U40" s="3">
+        <v>16729.407692307694</v>
       </c>
     </row>
   </sheetData>
